--- a/report-002-manual-002.xlsx
+++ b/report-002-manual-002.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "d887606be07d413c7c1920423ef6f89714d7989e", "fix_commit": "5576260b151fbacccf50f98ba716583fbd29d44b", "fix_passed": true, "red_failed": true, "test_commit": "f2060ac260ad81f5ea221f50a6bc3eb0f8ba2c8d"}</t>
+          <t>{"post_fix": {"commit": "5576260b151fbacccf50f98ba716583fbd29d44b", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "f2060ac260ad81f5ea221f50a6bc3eb0f8ba2c8d", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
